--- a/Docs/Test-Case/Test_Case_FE.xlsx
+++ b/Docs/Test-Case/Test_Case_FE.xlsx
@@ -1,26 +1,532 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KCPM - NAM3\Online-Store\Docs\Test-Case\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0417D38D-5018-41AE-8903-28BA2F0C480D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="107">
+  <si>
+    <t xml:space="preserve">Test case ID </t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_01</t>
+  </si>
+  <si>
+    <t>Test Summary</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_02</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_03</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_04</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa tên sản phẩm thành công.</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa giá sản phẩm hợp lệ.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee nhập giá sản phẩm âm.</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>BUG-EMP-01</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa mô tả sản phẩm.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_05</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_06</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_01</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_02</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_03</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_04</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_05</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa số lượng tồn kho.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa mô tả sản phẩm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager nhập giá sản phẩm âm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa giá sản phẩm hợp lệ.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa tên sản phẩm thành công.</t>
+  </si>
+  <si>
+    <t>BUG-MGR-01</t>
+  </si>
+  <si>
+    <t>FEATURE NOT AVAILABLE</t>
+  </si>
+  <si>
+    <t>TC_FE_NEG_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra chức năng Thêm sản phẩm không tồn tại trên giao diện.</t>
+  </si>
+  <si>
+    <t>BUG-NEG-01</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_07</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee xem danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager xem danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>EMPLOYEE</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Product.
+3. Chọn một sản phẩm bất kỳ.
+Nhấn nút Edit.
+4. Thay đổi Product Name từ "Core Java" thành "Core java ".
+5. Nhấn Save.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Employee.
+2. Chọn menu Orders.
+3. Quan sát danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Product.
+3. Chọn một sản phẩm bất kỳ.
+Nhấn nút Edit.
+4. Thay đổi Product Name từ "Core Java" thành "Core java ".
+5. Nhấn Save.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Manager.
+2. Chọn menu Orders.
+3. Quan sát danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn nút Edit.
+5. Nhập Product Price = 90.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Nhập Product Price = -30.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Sửa Product Description thành: "Books for learning Java language."
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Mở lại sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Thay đổi Product Stock từ 20 thành 50.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra số lượng tồn kho của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Orders.
+3. Chọn một đơn hàng có trạng thái New.
+4. Nhấn Finish.
+5. Quay lại danh sách đơn hàng.
+6. Kiểm tra trạng thái của đơn hàng vừa xử lý.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn nút Edit.
+5. Nhập Product Price = 90.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Nhập Product Price = -30.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Sửa Product Description thành: "Books for learning Java language."
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Mở lại sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Thay đổi Product Stock từ 20 thành 50.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra số lượng tồn kho của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Orders.
+3. Chọn một đơn hàng có trạng thái New.
+4. Nhấn Finish.
+5. Quay lại danh sách đơn hàng.
+6. Kiểm tra trạng thái của đơn hàng vừa xử lý.</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_06</t>
+  </si>
+  <si>
+    <t>- Hệ thống hiển thị danh sách đơn hàng.
+- Mỗi đơn hàng hiển thị đầy đủ các thông tin:
+  + Order ID.
+  + Customer Name.
+  + Customer Email.
+  + Customer Phone.
+  + Shipping Address.
+  + Total.
+  + Order Date.
+  + Status.
+  + Action.
+- Không có lỗi hiển thị.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Số lượng tồn kho hiển thị là 50.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Mô tả được lưu thành công.
+- Hiển thị đúng mô tả mới.
+- Sau khi tải lại trang vẫn giữ nguyên.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Tên sản phẩm được cập nhật thành "Core java".
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Đơn hàng chuyển sang trạng thái Finished.
+- Danh sách đơn hàng cập nhật trạng thái mới.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Không cho phép lưu.
+- Hiển thị thông báo lỗi.
+- Giá sản phẩm không thay đổi.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Giá sản phẩm được cập nhật thành 90.
+- Danh sách sản phẩm hiển thị đúng giá mới.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Không có nút Add Product.
+- Không có trang Create Product.
+- Không có route tạo sản phẩm.
+- Chức năng Thêm sản phẩm chỉ tồn tại ở API (POST /seller/product/new), không có giao diện Frontend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- Đã đăng nhập bằng tài khoản Employee.
+- Có ít nhất 1 sản phẩm trong hệ thống.
+- Employee đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm để chỉnh sửa.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái New.</t>
+  </si>
+  <si>
+    <t>- Hệ thống hoạt động bình thường.
+- Đã đăng nhập bằng tài khoản Manager.
+- Có ít nhất 1 sản phẩm trong hệ thống.
+- Manager đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có sản phẩm để chỉnh sửa.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có sản phẩm.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái New.</t>
+  </si>
+  <si>
+    <t>- Đăng nhập bằng Manager.
+- Truy cập trang Product Management.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Mở trang Product Management.
+3. Quan sát toàn bộ giao diện.
+4. Kiểm tra thanh menu.
+5. Kiểm tra các nút chức năng.
+6. Kiểm tra URL.
+7. Kiểm tra DevTools (Network) khi thao tác.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra Employee xem chi tiết đơn hàng  </t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa số lượng tồn kho</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng.</t>
+  </si>
+  <si>
+    <t>- Hệ thống mở trang hoặc hộp thoại chi tiết đơn hàng.
+- Hiển thị đầy đủ các thông tin:
+  + Order ID.
+  + Customer Name.
+  + Customer Email.
+  + Customer Phone.
+  + Shipping Address.
+  + Total.
+  + Order Date.
+  + Status.
+  + Action.
+- Không có lỗi hiển thị.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_08</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái New</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái fíhined</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Finished.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Employee.
+2. Chọn menu Orders
+3. Chọn một đơn hàng có nút Show
+4. Nhấn show và xem</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Finished</t>
+  </si>
+  <si>
+    <t>- Cột Action chỉ hiện "Show"
+- Employee không thể hoàn tất hay xóa đơn hàng đã hoàn thành.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_09</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Cenceled.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Cột Action chỉ hiện "Show"
+- Employee không thể hoàn tất hay xóa đơn hàng đã xóa.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra Manager xem chi tiết đơn hàng  </t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái New</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái fíhined</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Finished.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Manager.
+2. Chọn menu Orders
+3. Chọn một đơn hàng có nút Show
+4. Nhấn show và xem</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Finished</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Cenceled.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Cenceled</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_09</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_10</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_08</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_07</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +534,77 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF11100E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,12 +612,178 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +1063,561 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29" style="37" customWidth="1"/>
+    <col min="2" max="2" width="68" style="37" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" style="37" customWidth="1"/>
+    <col min="4" max="4" width="52.77734375" style="37" customWidth="1"/>
+    <col min="5" max="5" width="47.77734375" style="37" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="37"/>
+    <col min="7" max="7" width="16.109375" style="37" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="38"/>
+    </row>
+    <row r="4" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="38"/>
+    </row>
+    <row r="5" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="38"/>
+    </row>
+    <row r="6" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="38"/>
+    </row>
+    <row r="7" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="38"/>
+    </row>
+    <row r="8" spans="1:8" ht="250.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="38"/>
+    </row>
+    <row r="9" spans="1:8" ht="250.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="38"/>
+    </row>
+    <row r="11" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="38"/>
+    </row>
+    <row r="12" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="38"/>
+    </row>
+    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="38"/>
+    </row>
+    <row r="15" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="38"/>
+    </row>
+    <row r="17" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="23"/>
+      <c r="H17" s="38"/>
+    </row>
+    <row r="18" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="38"/>
+    </row>
+    <row r="19" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23"/>
+      <c r="H19" s="38"/>
+    </row>
+    <row r="20" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="23"/>
+      <c r="H20" s="38"/>
+    </row>
+    <row r="21" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="23"/>
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="38"/>
+    </row>
+    <row r="23" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="38"/>
+    </row>
+    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="38"/>
+    </row>
+    <row r="25" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="38"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="38"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="38"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Docs/Test-Case/Test_Case_FE.xlsx
+++ b/Docs/Test-Case/Test_Case_FE.xlsx
@@ -1,26 +1,532 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KCPM - NAM3\Online-Store\Docs\Test-Case\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{018C0F26-5B51-4435-B2D6-4AF4252FFDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="6288" yWindow="1956" windowWidth="10332" windowHeight="8088" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="107">
+  <si>
+    <t xml:space="preserve">Test case ID </t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_01</t>
+  </si>
+  <si>
+    <t>Test Summary</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_02</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_03</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_04</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa tên sản phẩm thành công.</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa giá sản phẩm hợp lệ.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee nhập giá sản phẩm âm.</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>BUG-EMP-01</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa mô tả sản phẩm.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_05</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_06</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_01</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_02</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_03</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_04</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_05</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa số lượng tồn kho.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa mô tả sản phẩm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager nhập giá sản phẩm âm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa giá sản phẩm hợp lệ.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa tên sản phẩm thành công.</t>
+  </si>
+  <si>
+    <t>BUG-MGR-01</t>
+  </si>
+  <si>
+    <t>FEATURE NOT AVAILABLE</t>
+  </si>
+  <si>
+    <t>TC_FE_NEG_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra chức năng Thêm sản phẩm không tồn tại trên giao diện.</t>
+  </si>
+  <si>
+    <t>BUG-NEG-01</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_07</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee xem danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager xem danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>EMPLOYEE</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Product.
+3. Chọn một sản phẩm bất kỳ.
+Nhấn nút Edit.
+4. Thay đổi Product Name từ "Core Java" thành "Core java ".
+5. Nhấn Save.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Employee.
+2. Chọn menu Orders.
+3. Quan sát danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Product.
+3. Chọn một sản phẩm bất kỳ.
+Nhấn nút Edit.
+4. Thay đổi Product Name từ "Core Java" thành "Core java ".
+5. Nhấn Save.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Manager.
+2. Chọn menu Orders.
+3. Quan sát danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn nút Edit.
+5. Nhập Product Price = 90.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Nhập Product Price = -30.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Sửa Product Description thành: "Books for learning Java language."
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Mở lại sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Thay đổi Product Stock từ 20 thành 50.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra số lượng tồn kho của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Orders.
+3. Chọn một đơn hàng có trạng thái New.
+4. Nhấn Finish.
+5. Quay lại danh sách đơn hàng.
+6. Kiểm tra trạng thái của đơn hàng vừa xử lý.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn nút Edit.
+5. Nhập Product Price = 90.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Nhập Product Price = -30.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Sửa Product Description thành: "Books for learning Java language."
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Mở lại sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Thay đổi Product Stock từ 20 thành 50.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra số lượng tồn kho của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Orders.
+3. Chọn một đơn hàng có trạng thái New.
+4. Nhấn Finish.
+5. Quay lại danh sách đơn hàng.
+6. Kiểm tra trạng thái của đơn hàng vừa xử lý.</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_06</t>
+  </si>
+  <si>
+    <t>- Hệ thống hiển thị danh sách đơn hàng.
+- Mỗi đơn hàng hiển thị đầy đủ các thông tin:
+  + Order ID.
+  + Customer Name.
+  + Customer Email.
+  + Customer Phone.
+  + Shipping Address.
+  + Total.
+  + Order Date.
+  + Status.
+  + Action.
+- Không có lỗi hiển thị.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Số lượng tồn kho hiển thị là 50.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Mô tả được lưu thành công.
+- Hiển thị đúng mô tả mới.
+- Sau khi tải lại trang vẫn giữ nguyên.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Tên sản phẩm được cập nhật thành "Core java".
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Đơn hàng chuyển sang trạng thái Finished.
+- Danh sách đơn hàng cập nhật trạng thái mới.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Không cho phép lưu.
+- Hiển thị thông báo lỗi.
+- Giá sản phẩm không thay đổi.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Giá sản phẩm được cập nhật thành 90.
+- Danh sách sản phẩm hiển thị đúng giá mới.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Không có nút Add Product.
+- Không có trang Create Product.
+- Không có route tạo sản phẩm.
+- Chức năng Thêm sản phẩm chỉ tồn tại ở API (POST /seller/product/new), không có giao diện Frontend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- Đã đăng nhập bằng tài khoản Employee.
+- Có ít nhất 1 sản phẩm trong hệ thống.
+- Employee đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm để chỉnh sửa.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái New.</t>
+  </si>
+  <si>
+    <t>- Hệ thống hoạt động bình thường.
+- Đã đăng nhập bằng tài khoản Manager.
+- Có ít nhất 1 sản phẩm trong hệ thống.
+- Manager đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có sản phẩm để chỉnh sửa.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có sản phẩm.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái New.</t>
+  </si>
+  <si>
+    <t>- Đăng nhập bằng Manager.
+- Truy cập trang Product Management.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Mở trang Product Management.
+3. Quan sát toàn bộ giao diện.
+4. Kiểm tra thanh menu.
+5. Kiểm tra các nút chức năng.
+6. Kiểm tra URL.
+7. Kiểm tra DevTools (Network) khi thao tác.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra Employee xem chi tiết đơn hàng  </t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa số lượng tồn kho</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng.</t>
+  </si>
+  <si>
+    <t>- Hệ thống mở trang hoặc hộp thoại chi tiết đơn hàng.
+- Hiển thị đầy đủ các thông tin:
+  + Order ID.
+  + Customer Name.
+  + Customer Email.
+  + Customer Phone.
+  + Shipping Address.
+  + Total.
+  + Order Date.
+  + Status.
+  + Action.
+- Không có lỗi hiển thị.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_08</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái New</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái fíhined</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Finished.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Employee.
+2. Chọn menu Orders
+3. Chọn một đơn hàng có nút Show
+4. Nhấn show và xem</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Finished</t>
+  </si>
+  <si>
+    <t>- Cột Action chỉ hiện "Show"
+- Employee không thể hoàn tất hay xóa đơn hàng đã hoàn thành.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_09</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Cenceled.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Cột Action chỉ hiện "Show"
+- Employee không thể hoàn tất hay xóa đơn hàng đã xóa.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra Manager xem chi tiết đơn hàng  </t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái New</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái fíhined</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Finished.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Manager.
+2. Chọn menu Orders
+3. Chọn một đơn hàng có nút Show
+4. Nhấn show và xem</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Finished</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Cenceled.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Cenceled</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_09</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_10</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_08</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_07</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +534,77 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF11100E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,12 +612,178 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +1063,561 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29" style="37" customWidth="1"/>
+    <col min="2" max="2" width="68" style="37" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" style="37" customWidth="1"/>
+    <col min="4" max="4" width="52.77734375" style="37" customWidth="1"/>
+    <col min="5" max="5" width="47.77734375" style="37" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="37"/>
+    <col min="7" max="7" width="29.44140625" style="37" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="38"/>
+    </row>
+    <row r="4" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="38"/>
+    </row>
+    <row r="5" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="38"/>
+    </row>
+    <row r="6" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="38"/>
+    </row>
+    <row r="7" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="38"/>
+    </row>
+    <row r="8" spans="1:8" ht="250.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="38"/>
+    </row>
+    <row r="9" spans="1:8" ht="250.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="38"/>
+    </row>
+    <row r="11" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="38"/>
+    </row>
+    <row r="12" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="38"/>
+    </row>
+    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="38"/>
+    </row>
+    <row r="15" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="38"/>
+    </row>
+    <row r="17" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="23"/>
+      <c r="H17" s="38"/>
+    </row>
+    <row r="18" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="38"/>
+    </row>
+    <row r="19" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23"/>
+      <c r="H19" s="38"/>
+    </row>
+    <row r="20" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="23"/>
+      <c r="H20" s="38"/>
+    </row>
+    <row r="21" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="23"/>
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="38"/>
+    </row>
+    <row r="23" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="38"/>
+    </row>
+    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="38"/>
+    </row>
+    <row r="25" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="38"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="38"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="38"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Docs/Test-Case/Test_Case_FE.xlsx
+++ b/Docs/Test-Case/Test_Case_FE.xlsx
@@ -1,26 +1,893 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10802"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/Test-Case/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CD2538-240B-3B40-9526-FE18EC3B4F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="208">
+  <si>
+    <t xml:space="preserve">Test case ID </t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_01</t>
+  </si>
+  <si>
+    <t>Test Summary</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_02</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_03</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_04</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa tên sản phẩm thành công.</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa giá sản phẩm hợp lệ.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee nhập giá sản phẩm âm.</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>BUG-EMP-01</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa mô tả sản phẩm.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_05</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_06</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_01</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_02</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_03</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_04</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_05</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa số lượng tồn kho.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa mô tả sản phẩm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager nhập giá sản phẩm âm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa giá sản phẩm hợp lệ.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager chỉnh sửa tên sản phẩm thành công.</t>
+  </si>
+  <si>
+    <t>BUG-MGR-01</t>
+  </si>
+  <si>
+    <t>FEATURE NOT AVAILABLE</t>
+  </si>
+  <si>
+    <t>TC_FE_NEG_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra chức năng Thêm sản phẩm không tồn tại trên giao diện.</t>
+  </si>
+  <si>
+    <t>BUG-NEG-01</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_07</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee xem danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager xem danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>EMPLOYEE</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Product.
+3. Chọn một sản phẩm bất kỳ.
+Nhấn nút Edit.
+4. Thay đổi Product Name từ "Core Java" thành "Core java ".
+5. Nhấn Save.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Employee.
+2. Chọn menu Orders.
+3. Quan sát danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Product.
+3. Chọn một sản phẩm bất kỳ.
+Nhấn nút Edit.
+4. Thay đổi Product Name từ "Core Java" thành "Core java ".
+5. Nhấn Save.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Manager.
+2. Chọn menu Orders.
+3. Quan sát danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn nút Edit.
+5. Nhập Product Price = 90.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Nhập Product Price = -30.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Sửa Product Description thành: "Books for learning Java language."
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Mở lại sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Thay đổi Product Stock từ 20 thành 50.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra số lượng tồn kho của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Orders.
+3. Chọn một đơn hàng có trạng thái New.
+4. Nhấn Finish.
+5. Quay lại danh sách đơn hàng.
+6. Kiểm tra trạng thái của đơn hàng vừa xử lý.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn nút Edit.
+5. Nhập Product Price = 90.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Nhập Product Price = -30.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra giá của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Sửa Product Description thành: "Books for learning Java language."
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Mở lại sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Truy cập trang Product Management.
+3. Chọn một sản phẩm bất kỳ.
+4. Nhấn Edit.
+5. Thay đổi Product Stock từ 20 thành 50.
+6. Nhấn Save.
+7. Quay lại danh sách sản phẩm.
+8. Kiểm tra số lượng tồn kho của sản phẩm vừa chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Orders.
+3. Chọn một đơn hàng có trạng thái New.
+4. Nhấn Finish.
+5. Quay lại danh sách đơn hàng.
+6. Kiểm tra trạng thái của đơn hàng vừa xử lý.</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_06</t>
+  </si>
+  <si>
+    <t>- Hệ thống hiển thị danh sách đơn hàng.
+- Mỗi đơn hàng hiển thị đầy đủ các thông tin:
+  + Order ID.
+  + Customer Name.
+  + Customer Email.
+  + Customer Phone.
+  + Shipping Address.
+  + Total.
+  + Order Date.
+  + Status.
+  + Action.
+- Không có lỗi hiển thị.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Số lượng tồn kho hiển thị là 50.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Mô tả được lưu thành công.
+- Hiển thị đúng mô tả mới.
+- Sau khi tải lại trang vẫn giữ nguyên.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Tên sản phẩm được cập nhật thành "Core java".
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Đơn hàng chuyển sang trạng thái Finished.
+- Danh sách đơn hàng cập nhật trạng thái mới.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Không cho phép lưu.
+- Hiển thị thông báo lỗi.
+- Giá sản phẩm không thay đổi.</t>
+  </si>
+  <si>
+    <t>- Hệ thống lưu thành công.
+- Giá sản phẩm được cập nhật thành 90.
+- Danh sách sản phẩm hiển thị đúng giá mới.
+- Không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>- Không có nút Add Product.
+- Không có trang Create Product.
+- Không có route tạo sản phẩm.
+- Chức năng Thêm sản phẩm chỉ tồn tại ở API (POST /seller/product/new), không có giao diện Frontend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- Đã đăng nhập bằng tài khoản Employee.
+- Có ít nhất 1 sản phẩm trong hệ thống.
+- Employee đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm để chỉnh sửa.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có sản phẩm.</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái New.</t>
+  </si>
+  <si>
+    <t>- Hệ thống hoạt động bình thường.
+- Đã đăng nhập bằng tài khoản Manager.
+- Có ít nhất 1 sản phẩm trong hệ thống.
+- Manager đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có sản phẩm để chỉnh sửa.
+- Đang ở màn hình Edit Product.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có sản phẩm.</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái New.</t>
+  </si>
+  <si>
+    <t>- Đăng nhập bằng Manager.
+- Truy cập trang Product Management.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Mở trang Product Management.
+3. Quan sát toàn bộ giao diện.
+4. Kiểm tra thanh menu.
+5. Kiểm tra các nút chức năng.
+6. Kiểm tra URL.
+7. Kiểm tra DevTools (Network) khi thao tác.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra Employee xem chi tiết đơn hàng  </t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee chỉnh sửa số lượng tồn kho</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng.</t>
+  </si>
+  <si>
+    <t>- Hệ thống mở trang hoặc hộp thoại chi tiết đơn hàng.
+- Hiển thị đầy đủ các thông tin:
+  + Order ID.
+  + Customer Name.
+  + Customer Email.
+  + Customer Phone.
+  + Shipping Address.
+  + Total.
+  + Order Date.
+  + Status.
+  + Action.
+- Không có lỗi hiển thị.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_08</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái New</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái fíhined</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Finished.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Employee.
+2. Chọn menu Orders
+3. Chọn một đơn hàng có nút Show
+4. Nhấn show và xem</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Finished</t>
+  </si>
+  <si>
+    <t>- Cột Action chỉ hiện "Show"
+- Employee không thể hoàn tất hay xóa đơn hàng đã hoàn thành.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_09</t>
+  </si>
+  <si>
+    <t>Kiểm tra Employee hoàn tất đơn hàng.ở trạng thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Employee đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Cenceled.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Employee.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Cột Action chỉ hiện "Show"
+- Employee không thể hoàn tất hay xóa đơn hàng đã xóa.</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra Manager xem chi tiết đơn hàng  </t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái New</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái fíhined</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Finished.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập Manager.
+2. Chọn menu Orders
+3. Chọn một đơn hàng có nút Show
+4. Nhấn show và xem</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Finished</t>
+  </si>
+  <si>
+    <t>Kiểm tra Manager hoàn tất đơn hàng.ở trạng thái Cenceled</t>
+  </si>
+  <si>
+    <t>- Manager đã đăng nhập.
+- Có ít nhất một đơn hàng ở trạng thái Cenceled.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập bằng tài khoản Manager.
+2. Chọn menu Oders
+3. Quan sát đơn hàng có trang thái Cenceled</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_09</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_10</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_08</t>
+  </si>
+  <si>
+    <t>TC_FE_MRG_07</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_01</t>
+  </si>
+  <si>
+    <t>Đăng ký với dữ liệu hợp lệ (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Form gửi thành công. Chuyển hướng sang trang /login. Người dùng có thể đăng nhập bằng tài khoản mới. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: newuser@email.com. 
+2. Nhập Name: Test User.
+3. Nhập Password: pass123. 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 123 Test Street. 
+6. Nhấn Sign Up.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_02</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_03</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_04</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_05</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_06</t>
+  </si>
+  <si>
+    <t>Đăng ký với email trùng lặp (EP — phân vùng trùng lặp)</t>
+  </si>
+  <si>
+    <t>Tài khoản customer1@email.com đã tồn tại. Người dùng đang ở trang /register.</t>
+  </si>
+  <si>
+    <t>API trả lỗi (HTTP 500 do bug đã biết). Người dùng KHÔNG được chuyển sang trang đăng nhập. Đăng ký thất bại. (REQ-AUTH-01, Bug đã biết #2)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: customer1@email.com. 
+2. Nhập Name: Duplicate User. 
+3. Nhập Password: pass123. 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 456 Dup Street. 
+6. Nhấn Sign Up.</t>
+  </si>
+  <si>
+    <t>Đăng ký với định dạng email không hợp lệ (EP — phân vùng không hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang /register.</t>
+  </si>
+  <si>
+    <t>Trường Email hiển thị lỗi "Invalid Email". Nút Sign Up vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: not-an-email. 
+2. Nhập Name: Test User. 
+3. Nhập Password: pass123. 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 123 Test Street. 
+6. Quan sát validation của form.</t>
+  </si>
+  <si>
+    <t>Đăng ký với các trường bắt buộc để trống (EP — phân vùng trống)</t>
+  </si>
+  <si>
+    <t>Mỗi trường bắt buộc hiển thị lỗi "X is required". Nút Sign Up vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>1. Để trống tất cả các trường. 
+2. Click vào từng trường rồi click ra ngoài. 
+3. Quan sát các thông báo lỗi.</t>
+  </si>
+  <si>
+    <t>Đăng ký với mật khẩu dưới độ dài tối thiểu (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>Trường Password hiển thị lỗi "Password must be at least 3 characters long". Nút Sign Up vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: bva@email.com. 
+2. Nhập Name: BVA User. 
+3. Nhập Password: ab (2 ký tự, dưới minlength=3). 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 789 BVA Street. 
+6. Quan sát validation của form.</t>
+  </si>
+  <si>
+    <t>Đăng ký với mật khẩu đúng độ dài tối thiểu (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>Form gửi thành công. Chuyển hướng sang trang /login. Không có lỗi validation trên trường mật khẩu. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: bva2@email.com. 
+2. Nhập Name: BVA User 2. 
+3. Nhập Password: abc (3 ký tự, đúng minlength=3). 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 321 BVA Street. 
+6. Nhấn Sign Up.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_01</t>
+  </si>
+  <si>
+    <t>Đăng nhập với tài khoản Customer hợp lệ (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang /login. Tài khoản customer1@email.com / 123 tồn tại.</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công. JWT token được lưu trong localStorage. Chuyển hướng về / (danh sách sản phẩm). Thanh điều hướng hiển thị tên người dùng, Cart, Orders, Sign Out. (REQ-AUTH-03)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: customer1@email.com. 
+2. Nhập Password: 123. 
+3. Nhấn Sign In.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_02</t>
+  </si>
+  <si>
+    <t>Đăng nhập với mật khẩu sai (EP — phân vùng không hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang /login.</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Invalid username and password.". Người dùng vẫn ở trang /login. Không lưu token. (REQ-AUTH-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_03</t>
+  </si>
+  <si>
+    <t>Đăng nhập với các trường để trống (EP — phân vùng trống)</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi "Email is required". Nút Sign In vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_04</t>
+  </si>
+  <si>
+    <t>Đăng xuất xóa phiên và chuyển hướng (REQ-AUTH-04)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Người dùng đang ở bất kỳ trang nào.</t>
+  </si>
+  <si>
+    <t>JWT token bị xóa khỏi localStorage. Chuyển hướng về trang /login với ?logout=true. Hiển thị thông báo "You have been logged out.". Truy cập /cart sẽ chuyển về /login. (REQ-AUTH-04)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: customer1@email.com. 
+2. Nhập Password: wrongpass. 
+3. Nhấn Sign In.</t>
+  </si>
+  <si>
+    <t>1. Để trống Email và Password. 
+2. Quan sát validation của form.
+3. Nhấn Sign In (nút nên bị vô hiệu hóa).</t>
+  </si>
+  <si>
+    <t>1. Nhấn Sign Out trên thanh điều hướng. 
+2. Quan sát chuyển trang.
+3. Thử truy cập /cart trực tiếp qua URL.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_01</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ từ trang chi tiết (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Sản phẩm B0001 (Core Java) có tồn kho &gt; 0. Người dùng đang ở /product/B0001.</t>
+  </si>
+  <si>
+    <t>Chuyển hướng về /cart. Giỏ hàng hiển thị sản phẩm B0001 với số lượng = 2. Thành tiền = giá × 2. Tổng giỏ hàng được cập nhật đúng. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_02</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm với số lượng vượt tồn kho (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Sản phẩm B0001 có tồn kho = 96. Người dùng đang ở /product/B0001.</t>
+  </si>
+  <si>
+    <t>validateCount() tự động hạ số lượng xuống 96 (max = productStock). Không hiển thị thông báo lỗi. Người dùng có thể thêm vào giỏ với số lượng = 96. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_03</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm với số lượng ở giới hạn tối thiểu (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Người dùng đang ở /product/B0001.</t>
+  </si>
+  <si>
+    <t>Sản phẩm được thêm vào giỏ với số lượng = 1. Chuyển hướng về /cart. Thành tiền = giá × 1. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_04</t>
+  </si>
+  <si>
+    <t>Cập nhật số lượng sản phẩm trong giỏ bằng nút +/- (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Giỏ hàng có sản phẩm B0001 với số lượng = 2. Người dùng đang ở /cart.</t>
+  </si>
+  <si>
+    <t>Sau khi nhấn +: số lượng = 3, thành tiền cập nhật. Sau khi nhấn −: số lượng = 2, thành tiền cập nhật. Server cart được cập nhật (PUT /cart/{itemId}). (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>1. Kiểm tra tên sản phẩm, giá, tồn kho được hiển thị. 
+2. Đặt số lượng input = 2. 
+3. Nhấn Add to Cart.</t>
+  </si>
+  <si>
+    <t>1. Nhập Số lượng = 97 (vượt tồn kho 96). 
+2. Click vào trường input hoặc nhấn Tab để kích hoạt validateCount(). 
+3. Quan sát giá trị số lượng.</t>
+  </si>
+  <si>
+    <t>1. Nhập Số lượng = 1 (tối thiểu cho phép, min=1). 
+2. Nhấn Add to Cart.</t>
+  </si>
+  <si>
+    <t>1. Nhấn nút + trên dòng B0001. 
+2. Quan sát số lượng và thành tiền. 
+3. Nhấn nút −. 
+4. Quan sát số lượng và thành tiền.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_05</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm khỏi giỏ hàng (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Giỏ hàng có sản phẩm B0001. Người dùng đang ở /cart.</t>
+  </si>
+  <si>
+    <t>Dòng B0001 biến mất khỏi giỏ. Tổng giỏ hàng được tính lại. Server cart được cập nhật (DELETE /cart/{itemId}). (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>1. Nhấn Remove trên dòng B0001. 
+2. Quan sát bảng giỏ hàng.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_06</t>
+  </si>
+  <si>
+    <t>Giỏ hàng khách merge vào server cart khi đăng nhập (REQ-CART-02)</t>
+  </si>
+  <si>
+    <t>Người dùng CHƯA đăng nhập. Sản phẩm B0001 đã thêm vào local cart (cookie).</t>
+  </si>
+  <si>
+    <t>Sản phẩm trong local cart (B0001, sl=1) được merge vào server cart (POST /cart). Trang giỏ hàng hiển thị B0001 với số lượng = 1. Cookie local cart bị xóa. (REQ-CART-02)</t>
+  </si>
+  <si>
+    <t>1. Với tư cách khách, truy cập /product/B0001. 
+2. Đặt Số lượng = 1, nhấn Add to Cart.
+3. Truy cập /cart, xác nhận sản phẩm có trong local cart. 
+4. Nhấn Sign In, đăng nhập customer1@email.com / 123. 
+5. Truy cập /cart.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_01</t>
+  </si>
+  <si>
+    <t>Thanh toán khi có sản phẩm trong giỏ (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập customer1@email.com. Giỏ có sản phẩm B0001 (sl=1, giá=$30).</t>
+  </si>
+  <si>
+    <t>Giỏ hàng được xóa (POST /cart/checkout). Chuyển hướng về / (trang chủ). Đơn hàng mới được tạo với trạng thái = New (0). (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_02</t>
+  </si>
+  <si>
+    <t>Thanh toán khi giỏ hàng trống (EP — phân vùng trống)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập với tư cách Customer. Giỏ hàng trống.</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo "Cart is empty. Go to get something! :)". Không có nút Checkout hiển thị. Không thể thanh toán. (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_03</t>
+  </si>
+  <si>
+    <t>Thanh toán chuyển hướng người chưa đăng nhập về trang login (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>Người dùng CHƯA đăng nhập. Giỏ hàng có sản phẩm (local/cookie).</t>
+  </si>
+  <si>
+    <t>Chuyển hướng về /login?returnUrl=%2Fcart. Sau khi đăng nhập, chuyển về lại /cart. (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_04</t>
+  </si>
+  <si>
+    <t>Customer xem đơn hàng của mình sau khi thanh toán (REQ-ORD-01)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập customer1@email.com. Người dùng đã đặt ít nhất 1 đơn hàng.</t>
+  </si>
+  <si>
+    <t>Trang danh sách đơn /order tải thành công. Bảng hiển thị: Order #, Tên KH, Email, SĐT, Địa chỉ, Tổng tiền, Ngày đặt, Trạng thái. Chỉ hiển thị đơn hàng thuộc về customer1@email.com. (REQ-ORD-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_05</t>
+  </si>
+  <si>
+    <t>Customer hủy đơn hàng ở trạng thái New (REQ-ORD-02)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập customer1@email.com. Người dùng có đơn hàng với trạng thái = New (0).</t>
+  </si>
+  <si>
+    <t>Trạng thái đơn hàng chuyển từ "New" sang "Canceled". Bảng cập nhật hiển thị trạng thái mới. Nút Cancel biến mất cho đơn đó (trạng thái ≠ 0). (REQ-ORD-02)</t>
+  </si>
+  <si>
+    <t>1. Truy cập /cart. 
+2. Kiểm tra sản phẩm và tổng tiền hiển thị. 
+3. Nhấn Checkout. 
+4. Quan sát chuyển trang.</t>
+  </si>
+  <si>
+    <t>1. Truy cập /cart. 
+2. Quan sát thông báo giỏ trống. 
+3. Kiểm tra nút Checkout không hiển thị.</t>
+  </si>
+  <si>
+    <t>1. Truy cập /cart. 
+2. Nhấn Checkout.</t>
+  </si>
+  <si>
+    <t>1. Nhấn Orders trên thanh điều hướng. 
+2. Quan sát bảng danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Truy cập /order. 
+2. Tìm đơn hàng có trạng thái "New". 
+3. Nhấn Cancel.
+4. Quan sát cập nhật trạng thái.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +895,95 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF11100E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,12 +991,214 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +1478,1025 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29" style="37" customWidth="1"/>
+    <col min="2" max="2" width="68" style="37" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" style="37" customWidth="1"/>
+    <col min="4" max="4" width="52.83203125" style="37" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" style="37" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="37"/>
+    <col min="7" max="7" width="29.5" style="37" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="44"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+    </row>
+    <row r="4" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="46"/>
+      <c r="H4" s="38"/>
+    </row>
+    <row r="5" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="38"/>
+    </row>
+    <row r="6" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="48"/>
+      <c r="H6" s="38"/>
+    </row>
+    <row r="7" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="38"/>
+    </row>
+    <row r="8" spans="1:31" ht="250" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="48"/>
+      <c r="H8" s="38"/>
+    </row>
+    <row r="9" spans="1:31" ht="250" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="38"/>
+    </row>
+    <row r="10" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="48"/>
+      <c r="H10" s="38"/>
+    </row>
+    <row r="11" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="38"/>
+    </row>
+    <row r="12" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="48"/>
+      <c r="H12" s="38"/>
+    </row>
+    <row r="13" spans="1:31" ht="158" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="38"/>
+    </row>
+    <row r="14" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="48"/>
+      <c r="H14" s="38"/>
+    </row>
+    <row r="15" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:31" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="48"/>
+      <c r="H16" s="38"/>
+    </row>
+    <row r="17" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="38"/>
+    </row>
+    <row r="18" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="48"/>
+      <c r="H18" s="38"/>
+    </row>
+    <row r="19" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="38"/>
+    </row>
+    <row r="20" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="48"/>
+      <c r="H20" s="38"/>
+    </row>
+    <row r="21" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="48"/>
+      <c r="H22" s="38"/>
+    </row>
+    <row r="23" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="38"/>
+    </row>
+    <row r="24" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="38"/>
+    </row>
+    <row r="25" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="38"/>
+    </row>
+    <row r="26" spans="1:8" ht="144" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="9"/>
+      <c r="H26" s="38"/>
+    </row>
+    <row r="27" spans="1:8" ht="144" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="162" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" ht="162" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" ht="234" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="234" x14ac:dyDescent="0.2">
+      <c r="A31" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:8" ht="108" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" spans="1:7" ht="144" x14ac:dyDescent="0.2">
+      <c r="A37" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" spans="1:7" ht="144" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="162" x14ac:dyDescent="0.2">
+      <c r="A39" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="23"/>
+    </row>
+    <row r="40" spans="1:7" ht="162" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" ht="234" x14ac:dyDescent="0.2">
+      <c r="A41" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" spans="1:7" ht="234" x14ac:dyDescent="0.2">
+      <c r="A42" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" spans="1:7" ht="108" x14ac:dyDescent="0.2">
+      <c r="A43" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="23"/>
+    </row>
+    <row r="44" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="5"/>
+    </row>
+    <row r="45" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="30"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="32"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="36"/>
+    </row>
+    <row r="47" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Docs/Test-Case/Test_Case_FE.xlsx
+++ b/Docs/Test-Case/Test_Case_FE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KCPM - NAM3\Online-Store\Docs\Test-Case\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/Test-Case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{018C0F26-5B51-4435-B2D6-4AF4252FFDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A636434D-B3D2-0D4E-9DA5-2E26B6933C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6288" yWindow="1956" windowWidth="10332" windowHeight="8088" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="208">
   <si>
     <t xml:space="preserve">Test case ID </t>
   </si>
@@ -520,6 +520,367 @@
   </si>
   <si>
     <t>TC_FE_MRG_07</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_01</t>
+  </si>
+  <si>
+    <t>Đăng ký với dữ liệu hợp lệ (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Form gửi thành công. Chuyển hướng sang trang /login. Người dùng có thể đăng nhập bằng tài khoản mới. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_02</t>
+  </si>
+  <si>
+    <t>Đăng ký với email trùng lặp (EP — phân vùng trùng lặp)</t>
+  </si>
+  <si>
+    <t>Tài khoản customer1@email.com đã tồn tại. Người dùng đang ở trang /register.</t>
+  </si>
+  <si>
+    <t>API trả lỗi (HTTP 500 do bug đã biết). Người dùng KHÔNG được chuyển sang trang đăng nhập. Đăng ký thất bại. (REQ-AUTH-01, Bug đã biết #2)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_03</t>
+  </si>
+  <si>
+    <t>Đăng ký với định dạng email không hợp lệ (EP — phân vùng không hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang /register.</t>
+  </si>
+  <si>
+    <t>Trường Email hiển thị lỗi "Invalid Email". Nút Sign Up vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_04</t>
+  </si>
+  <si>
+    <t>Đăng ký với các trường bắt buộc để trống (EP — phân vùng trống)</t>
+  </si>
+  <si>
+    <t>Mỗi trường bắt buộc hiển thị lỗi "X is required". Nút Sign Up vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_05</t>
+  </si>
+  <si>
+    <t>Đăng ký với mật khẩu dưới độ dài tối thiểu (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>Trường Password hiển thị lỗi "Password must be at least 3 characters long". Nút Sign Up vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: newuser@email.com. 
+2. Nhập Name: Test User.
+3. Nhập Password: pass123. 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 123 Test Street. 
+6. Nhấn Sign Up.</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: customer1@email.com. 
+2. Nhập Name: Duplicate User. 
+3. Nhập Password: pass123. 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 456 Dup Street. 
+6. Nhấn Sign Up.</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: not-an-email. 
+2. Nhập Name: Test User. 
+3. Nhập Password: pass123. 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 123 Test Street. 
+6. Quan sát validation của form.</t>
+  </si>
+  <si>
+    <t>1. Để trống tất cả các trường. 
+2. Click vào từng trường rồi click ra ngoài. 
+3. Quan sát các thông báo lỗi.</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: bva@email.com. 
+2. Nhập Name: BVA User. 
+3. Nhập Password: ab (2 ký tự, dưới minlength=3). 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 789 BVA Street. 
+6. Quan sát validation của form.</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_06</t>
+  </si>
+  <si>
+    <t>Đăng ký với mật khẩu đúng độ dài tối thiểu (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: bva2@email.com. 
+2. Nhập Name: BVA User 2. 
+3. Nhập Password: abc (3 ký tự, đúng minlength=3). 
+4. Nhập Phone: 0901234567. 
+5. Nhập Address: 321 BVA Street. 
+6. Nhấn Sign Up.</t>
+  </si>
+  <si>
+    <t>Form gửi thành công. Chuyển hướng sang trang /login. Không có lỗi validation trên trường mật khẩu. (REQ-AUTH-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_01</t>
+  </si>
+  <si>
+    <t>Đăng nhập với tài khoản Customer hợp lệ (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang /login. Tài khoản customer1@email.com / 123 tồn tại.</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: customer1@email.com. 
+2. Nhập Password: 123. 
+3. Nhấn Sign In.</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công. JWT token được lưu trong localStorage. Chuyển hướng về / (danh sách sản phẩm). Thanh điều hướng hiển thị tên người dùng, Cart, Orders, Sign Out. (REQ-AUTH-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_02</t>
+  </si>
+  <si>
+    <t>Đăng nhập với mật khẩu sai (EP — phân vùng không hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang /login.</t>
+  </si>
+  <si>
+    <t>1. Nhập Email: customer1@email.com. 
+2. Nhập Password: wrongpass. 
+3. Nhấn Sign In.</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Invalid username and password.". Người dùng vẫn ở trang /login. Không lưu token. (REQ-AUTH-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_03</t>
+  </si>
+  <si>
+    <t>Đăng nhập với các trường để trống (EP — phân vùng trống)</t>
+  </si>
+  <si>
+    <t>1. Để trống Email và Password. 
+2. Quan sát validation của form.
+3. Nhấn Sign In (nút nên bị vô hiệu hóa).</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi "Email is required". Nút Sign In vẫn bị vô hiệu hóa. Form không gửi đi. (REQ-AUTH-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_LOG_04</t>
+  </si>
+  <si>
+    <t>Đăng xuất xóa phiên và chuyển hướng (REQ-AUTH-04)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Người dùng đang ở bất kỳ trang nào.</t>
+  </si>
+  <si>
+    <t>1. Nhấn Sign Out trên thanh điều hướng. 
+2. Quan sát chuyển trang.
+3. Thử truy cập /cart trực tiếp qua URL.</t>
+  </si>
+  <si>
+    <t>JWT token bị xóa khỏi localStorage. Chuyển hướng về trang /login với ?logout=true. Hiển thị thông báo "You have been logged out.". Truy cập /cart sẽ chuyển về /login. (REQ-AUTH-04)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_01</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ từ trang chi tiết (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Sản phẩm B0001 (Core Java) có tồn kho &gt; 0. Người dùng đang ở /product/B0001.</t>
+  </si>
+  <si>
+    <t>1. Kiểm tra tên sản phẩm, giá, tồn kho được hiển thị. 
+2. Đặt số lượng input = 2. 
+3. Nhấn Add to Cart.</t>
+  </si>
+  <si>
+    <t>Chuyển hướng về /cart. Giỏ hàng hiển thị sản phẩm B0001 với số lượng = 2. Thành tiền = giá × 2. Tổng giỏ hàng được cập nhật đúng. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_02</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm với số lượng vượt tồn kho (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Sản phẩm B0001 có tồn kho = 96. Người dùng đang ở /product/B0001.</t>
+  </si>
+  <si>
+    <t>1. Nhập Số lượng = 97 (vượt tồn kho 96). 
+2. Click vào trường input hoặc nhấn Tab để kích hoạt validateCount(). 
+3. Quan sát giá trị số lượng.</t>
+  </si>
+  <si>
+    <t>validateCount() tự động hạ số lượng xuống 96 (max = productStock). Không hiển thị thông báo lỗi. Người dùng có thể thêm vào giỏ với số lượng = 96. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_03</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm với số lượng ở giới hạn tối thiểu (BVA — giá trị biên)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Người dùng đang ở /product/B0001.</t>
+  </si>
+  <si>
+    <t>1. Nhập Số lượng = 1 (tối thiểu cho phép, min=1). 
+2. Nhấn Add to Cart.</t>
+  </si>
+  <si>
+    <t>Sản phẩm được thêm vào giỏ với số lượng = 1. Chuyển hướng về /cart. Thành tiền = giá × 1. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_04</t>
+  </si>
+  <si>
+    <t>Cập nhật số lượng sản phẩm trong giỏ bằng nút +/- (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Giỏ hàng có sản phẩm B0001 với số lượng = 2. Người dùng đang ở /cart.</t>
+  </si>
+  <si>
+    <t>1. Nhấn nút + trên dòng B0001. 
+2. Quan sát số lượng và thành tiền. 
+3. Nhấn nút −. 
+4. Quan sát số lượng và thành tiền.</t>
+  </si>
+  <si>
+    <t>Sau khi nhấn +: số lượng = 3, thành tiền cập nhật. Sau khi nhấn −: số lượng = 2, thành tiền cập nhật. Server cart được cập nhật (PUT /cart/{itemId}). (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_05</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm khỏi giỏ hàng (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập với tư cách Customer. Giỏ hàng có sản phẩm B0001. Người dùng đang ở /cart.</t>
+  </si>
+  <si>
+    <t>1. Nhấn Remove trên dòng B0001. 
+2. Quan sát bảng giỏ hàng.</t>
+  </si>
+  <si>
+    <t>Dòng B0001 biến mất khỏi giỏ. Tổng giỏ hàng được tính lại. Server cart được cập nhật (DELETE /cart/{itemId}). (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CART_06</t>
+  </si>
+  <si>
+    <t>Giỏ hàng khách merge vào server cart khi đăng nhập (REQ-CART-02)</t>
+  </si>
+  <si>
+    <t>Người dùng CHƯA đăng nhập. Sản phẩm B0001 đã thêm vào local cart (cookie).</t>
+  </si>
+  <si>
+    <t>1. Với tư cách khách, truy cập /product/B0001. 
+2. Đặt Số lượng = 1, nhấn Add to Cart.
+3. Truy cập /cart, xác nhận sản phẩm có trong local cart. 
+4. Nhấn Sign In, đăng nhập customer1@email.com / 123. 
+5. Truy cập /cart.</t>
+  </si>
+  <si>
+    <t>Sản phẩm trong local cart (B0001, sl=1) được merge vào server cart (POST /cart). Trang giỏ hàng hiển thị B0001 với số lượng = 1. Cookie local cart bị xóa. (REQ-CART-02)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_01</t>
+  </si>
+  <si>
+    <t>Thanh toán khi có sản phẩm trong giỏ (EP — phân vùng hợp lệ)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập customer1@email.com. Giỏ có sản phẩm B0001 (sl=1, giá=$30).</t>
+  </si>
+  <si>
+    <t>1. Truy cập /cart. 
+2. Kiểm tra sản phẩm và tổng tiền hiển thị. 
+3. Nhấn Checkout. 
+4. Quan sát chuyển trang.</t>
+  </si>
+  <si>
+    <t>Giỏ hàng được xóa (POST /cart/checkout). Chuyển hướng về / (trang chủ). Đơn hàng mới được tạo với trạng thái = New (0). (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_02</t>
+  </si>
+  <si>
+    <t>Thanh toán khi giỏ hàng trống (EP — phân vùng trống)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập với tư cách Customer. Giỏ hàng trống.</t>
+  </si>
+  <si>
+    <t>1. Truy cập /cart. 
+2. Quan sát thông báo giỏ trống. 
+3. Kiểm tra nút Checkout không hiển thị.</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo "Cart is empty. Go to get something! :)". Không có nút Checkout hiển thị. Không thể thanh toán. (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_03</t>
+  </si>
+  <si>
+    <t>Thanh toán chuyển hướng người chưa đăng nhập về trang login (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>Người dùng CHƯA đăng nhập. Giỏ hàng có sản phẩm (local/cookie).</t>
+  </si>
+  <si>
+    <t>1. Truy cập /cart. 
+2. Nhấn Checkout.</t>
+  </si>
+  <si>
+    <t>Chuyển hướng về /login?returnUrl=%2Fcart. Sau khi đăng nhập, chuyển về lại /cart. (REQ-CART-03)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_04</t>
+  </si>
+  <si>
+    <t>Customer xem đơn hàng của mình sau khi thanh toán (REQ-ORD-01)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập customer1@email.com. Người dùng đã đặt ít nhất 1 đơn hàng.</t>
+  </si>
+  <si>
+    <t>1. Nhấn Orders trên thanh điều hướng. 
+2. Quan sát bảng danh sách đơn hàng.</t>
+  </si>
+  <si>
+    <t>Trang danh sách đơn /order tải thành công. Bảng hiển thị: Order #, Tên KH, Email, SĐT, Địa chỉ, Tổng tiền, Ngày đặt, Trạng thái. Chỉ hiển thị đơn hàng thuộc về customer1@email.com. (REQ-ORD-01)</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_05</t>
+  </si>
+  <si>
+    <t>Customer hủy đơn hàng ở trạng thái New (REQ-ORD-02)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập customer1@email.com. Người dùng có đơn hàng với trạng thái = New (0).</t>
+  </si>
+  <si>
+    <t>1. Truy cập /order. 
+2. Tìm đơn hàng có trạng thái "New". 
+3. Nhấn Cancel.
+4. Quan sát cập nhật trạng thái.</t>
+  </si>
+  <si>
+    <t>Trạng thái đơn hàng chuyển từ "New" sang "Canceled". Bảng cập nhật hiển thị trạng thái mới. Nút Cancel biến mất cho đơn đó (trạng thái ≠ 0). (REQ-ORD-02)</t>
   </si>
 </sst>
 </file>
@@ -560,7 +921,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -600,6 +961,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -782,6 +1155,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1064,20 +1470,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" style="37" customWidth="1"/>
     <col min="2" max="2" width="68" style="37" customWidth="1"/>
     <col min="3" max="3" width="45.6640625" style="37" customWidth="1"/>
-    <col min="4" max="4" width="52.77734375" style="37" customWidth="1"/>
-    <col min="5" max="5" width="47.77734375" style="37" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="37"/>
-    <col min="7" max="7" width="29.44140625" style="37" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="37"/>
+    <col min="4" max="4" width="52.83203125" style="37" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" style="37" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="37"/>
+    <col min="7" max="7" width="29.5" style="37" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1100,521 +1506,961 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="5"/>
+    <row r="2" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="42"/>
       <c r="H3" s="38"/>
     </row>
-    <row r="4" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="9"/>
+    <row r="4" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="45"/>
       <c r="H4" s="38"/>
     </row>
-    <row r="5" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>65</v>
+    <row r="5" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>16</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5"/>
       <c r="H5" s="38"/>
     </row>
-    <row r="6" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="9"/>
+    <row r="6" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="48"/>
       <c r="H6" s="38"/>
     </row>
-    <row r="7" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>66</v>
+    <row r="7" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="38"/>
     </row>
-    <row r="8" spans="1:8" ht="250.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:8" ht="250" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="48"/>
+      <c r="H8" s="38"/>
+    </row>
+    <row r="9" spans="1:8" ht="250" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="48"/>
+      <c r="H10" s="38"/>
+    </row>
+    <row r="11" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="38"/>
+    </row>
+    <row r="12" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="48"/>
+      <c r="H12" s="38"/>
+    </row>
+    <row r="13" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="48"/>
+      <c r="H14" s="38"/>
+    </row>
+    <row r="15" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="48"/>
+      <c r="H16" s="38"/>
+    </row>
+    <row r="17" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="38"/>
+    </row>
+    <row r="18" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="48"/>
+      <c r="H18" s="38"/>
+    </row>
+    <row r="19" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="38"/>
+    </row>
+    <row r="20" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="48"/>
+      <c r="H20" s="38"/>
+    </row>
+    <row r="21" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="48"/>
+      <c r="H22" s="38"/>
+    </row>
+    <row r="23" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="38"/>
+    </row>
+    <row r="24" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="38"/>
+    </row>
+    <row r="25" spans="1:8" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="38"/>
+    </row>
+    <row r="26" spans="1:8" ht="144" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="9"/>
+      <c r="H26" s="38"/>
+    </row>
+    <row r="27" spans="1:8" ht="144" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="162" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" ht="162" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" ht="216" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C30" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E30" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="38"/>
-    </row>
-    <row r="9" spans="1:8" ht="250.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+      <c r="F30" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="234" x14ac:dyDescent="0.2">
+      <c r="A31" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B31" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C31" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E31" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="38"/>
-    </row>
-    <row r="10" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="F31" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:8" ht="108" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C32" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D32" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E32" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="38"/>
-    </row>
-    <row r="11" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="F32" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E33" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="38"/>
-    </row>
-    <row r="12" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="F33" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B34" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C34" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D34" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E34" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="38"/>
-    </row>
-    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="F34" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="38"/>
-    </row>
-    <row r="14" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="B35" s="19"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="38"/>
-    </row>
-    <row r="15" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="F36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" spans="1:7" ht="144" x14ac:dyDescent="0.2">
+      <c r="A37" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B37" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C37" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D37" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E37" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="38"/>
-    </row>
-    <row r="16" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="F37" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" spans="1:7" ht="144" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C38" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F38" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="38"/>
-    </row>
-    <row r="17" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+    </row>
+    <row r="39" spans="1:7" ht="162" x14ac:dyDescent="0.2">
+      <c r="A39" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B39" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C39" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D39" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E39" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="38"/>
-    </row>
-    <row r="18" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="F39" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="23"/>
+    </row>
+    <row r="40" spans="1:7" ht="162" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C40" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E40" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="38"/>
-    </row>
-    <row r="19" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
+      <c r="F40" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" ht="216" x14ac:dyDescent="0.2">
+      <c r="A41" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B41" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C41" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D41" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E41" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="38"/>
-    </row>
-    <row r="20" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
+      <c r="F41" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" spans="1:7" ht="234" x14ac:dyDescent="0.2">
+      <c r="A42" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B42" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C42" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D42" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E42" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="38"/>
-    </row>
-    <row r="21" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="F42" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" spans="1:7" ht="108" x14ac:dyDescent="0.2">
+      <c r="A43" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B43" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C43" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D43" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E43" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="38"/>
-    </row>
-    <row r="22" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="F43" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="23"/>
+    </row>
+    <row r="44" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E44" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="38"/>
-    </row>
-    <row r="23" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
+      <c r="F44" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="5"/>
+    </row>
+    <row r="45" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B45" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C45" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D45" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E45" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="38"/>
-    </row>
-    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
+      <c r="F45" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="30"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="38"/>
-    </row>
-    <row r="25" spans="1:8" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="B46" s="32"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="36"/>
+    </row>
+    <row r="47" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E47" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F47" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G47" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="38"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
-      <c r="B26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="38"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
